--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,30 +440,37 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>最大堆叠数量</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -471,7 +478,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -479,7 +486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -487,7 +494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -495,7 +502,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -503,7 +510,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -511,7 +518,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -519,23 +526,23 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
         <v>999</v>
@@ -543,15 +550,15 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -559,7 +566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -567,15 +574,15 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
         <v>999</v>
@@ -583,7 +590,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="n">
         <v>999</v>
@@ -591,7 +598,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" t="n">
         <v>999</v>
@@ -599,7 +606,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
         <v>999</v>
@@ -607,7 +614,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" t="n">
         <v>999</v>
@@ -615,7 +622,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" t="n">
         <v>999</v>
@@ -623,7 +630,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" t="n">
         <v>999</v>
@@ -631,7 +638,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" t="n">
         <v>999</v>
@@ -639,7 +646,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
         <v>999</v>
@@ -647,7 +654,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30" t="n">
         <v>999</v>
@@ -655,7 +662,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" t="n">
         <v>999</v>
@@ -663,7 +670,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="n">
         <v>999</v>
@@ -671,17 +678,9 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" t="n">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>28</v>
-      </c>
-      <c r="B34" t="n">
         <v>999</v>
       </c>
     </row>

--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>max_statck_size</t>
+          <t>max_stack_size</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
